--- a/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
+++ b/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTA('Treatments'!C6:F16)/(ROWS('Treatments'!C6:F16)*COLUMNS('Treatments'!C6:F16))</f>
+        <f>COUNTA('Treatments'!C6:F15)/(ROWS('Treatments'!C6:F15)*COLUMNS('Treatments'!C6:F15))</f>
         <v/>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTA('Treatment content'!B6:G16)/(ROWS('Treatment content'!B6:G16)*COLUMNS('Treatment content'!B6:G16))</f>
+        <f>COUNTA('Treatment content'!B6:G15)/(ROWS('Treatment content'!B6:G15)*COLUMNS('Treatment content'!B6:G15))</f>
         <v/>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Beard Transplant</t>
+          <t>Beard &amp; Moustache Transplant</t>
         </is>
       </c>
       <c r="C7" s="12" t="n"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Moustache Transplant</t>
+          <t>Scar Hair Transplant</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Scar Hair Transplant</t>
+          <t>Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="C10" s="12" t="n"/>
@@ -3103,12 +3103,12 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Hair Transplant</t>
+          <t>Hair Treatments</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C12" s="12" t="n"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="C13" s="12" t="n"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="C14" s="12" t="n"/>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="C15" s="12" t="n"/>
@@ -3181,16 +3181,8 @@
       <c r="F15" s="12" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Hair Treatments</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="n"/>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="12" t="n"/>
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
@@ -3211,14 +3203,6 @@
       <c r="D18" s="12" t="n"/>
       <c r="E18" s="12" t="n"/>
       <c r="F18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3232,7 +3216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3352,7 +3336,7 @@
     <row r="7" ht="90" customHeight="1">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>Beard Transplant</t>
+          <t>Beard &amp; Moustache Transplant</t>
         </is>
       </c>
       <c r="B7" s="12" t="n"/>
@@ -3378,7 +3362,7 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Moustache Transplant</t>
+          <t>Scar Hair Transplant</t>
         </is>
       </c>
       <c r="B9" s="12" t="n"/>
@@ -3391,7 +3375,7 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Scar Hair Transplant</t>
+          <t>Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -3404,7 +3388,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -3417,7 +3401,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -3430,7 +3414,7 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -3443,7 +3427,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -3456,7 +3440,7 @@
     <row r="15" ht="90" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="B15" s="12" t="n"/>
@@ -3465,19 +3449,6 @@
       <c r="E15" s="12" t="n"/>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="90" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
+++ b/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTA('Treatments'!C6:F15)/(ROWS('Treatments'!C6:F15)*COLUMNS('Treatments'!C6:F15))</f>
+        <f>COUNTA('Treatments'!C6:F14)/(ROWS('Treatments'!C6:F14)*COLUMNS('Treatments'!C6:F14))</f>
         <v/>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTA('Treatment content'!B6:G15)/(ROWS('Treatment content'!B6:G15)*COLUMNS('Treatment content'!B6:G15))</f>
+        <f>COUNTA('Treatment content'!B6:G14)/(ROWS('Treatment content'!B6:G14)*COLUMNS('Treatment content'!B6:G14))</f>
         <v/>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Scar Hair Transplant</t>
+          <t>Scar &amp; Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -3087,12 +3087,12 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Hair Transplant</t>
+          <t>Hair Treatments</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C10" s="12" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="C12" s="12" t="n"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="C13" s="12" t="n"/>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="C14" s="12" t="n"/>
@@ -3165,16 +3165,8 @@
       <c r="F14" s="12" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Hair Treatments</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="n"/>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="12" t="n"/>
       <c r="D15" s="12" t="n"/>
       <c r="E15" s="12" t="n"/>
@@ -3195,14 +3187,6 @@
       <c r="D17" s="12" t="n"/>
       <c r="E17" s="12" t="n"/>
       <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3216,7 +3200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3362,7 +3346,7 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Scar Hair Transplant</t>
+          <t>Scar &amp; Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="B9" s="12" t="n"/>
@@ -3375,7 +3359,7 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -3388,7 +3372,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -3401,7 +3385,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -3414,7 +3398,7 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -3427,7 +3411,7 @@
     <row r="14" ht="90" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -3436,19 +3420,6 @@
       <c r="E14" s="12" t="n"/>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="90" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
+++ b/elite-plus/_docs/Elite-Plus-Clinic-Data-Intake.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTA('Treatments'!C6:F14)/(ROWS('Treatments'!C6:F14)*COLUMNS('Treatments'!C6:F14))</f>
+        <f>COUNTA('Treatments'!C6:F13)/(ROWS('Treatments'!C6:F13)*COLUMNS('Treatments'!C6:F13))</f>
         <v/>
       </c>
     </row>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTA('Treatment content'!B6:G14)/(ROWS('Treatment content'!B6:G14)*COLUMNS('Treatment content'!B6:G14))</f>
+        <f>COUNTA('Treatment content'!B6:G13)/(ROWS('Treatment content'!B6:G13)*COLUMNS('Treatment content'!B6:G13))</f>
         <v/>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>Eyebrow Transplant</t>
+          <t>Scar &amp; Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="C8" s="12" t="n"/>
@@ -3071,12 +3071,12 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Hair Transplant</t>
+          <t>Hair Treatments</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Scar &amp; Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C9" s="12" t="n"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="C10" s="12" t="n"/>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="C11" s="12" t="n"/>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="C12" s="12" t="n"/>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="C13" s="12" t="n"/>
@@ -3149,16 +3149,8 @@
       <c r="F13" s="12" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Hair Treatments</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
+      <c r="A14" s="12" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="12" t="n"/>
       <c r="D14" s="12" t="n"/>
       <c r="E14" s="12" t="n"/>
@@ -3179,14 +3171,6 @@
       <c r="D16" s="12" t="n"/>
       <c r="E16" s="12" t="n"/>
       <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3200,7 +3184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3333,7 +3317,7 @@
     <row r="8" ht="90" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Eyebrow Transplant</t>
+          <t>Scar &amp; Burn Scar Hair Transplant</t>
         </is>
       </c>
       <c r="B8" s="12" t="n"/>
@@ -3346,7 +3330,7 @@
     <row r="9" ht="90" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>Scar &amp; Burn Scar Hair Transplant</t>
+          <t>G-Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B9" s="12" t="n"/>
@@ -3359,7 +3343,7 @@
     <row r="10" ht="90" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>G-Cell Hair Therapy</t>
+          <t>Stem Cell Hair Therapy</t>
         </is>
       </c>
       <c r="B10" s="12" t="n"/>
@@ -3372,7 +3356,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Stem Cell Hair Therapy</t>
+          <t>Regenera Activa (confirm name)</t>
         </is>
       </c>
       <c r="B11" s="12" t="n"/>
@@ -3385,7 +3369,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Regenera Activa (confirm name)</t>
+          <t>PRP (Plasma) Hair Treatment</t>
         </is>
       </c>
       <c r="B12" s="12" t="n"/>
@@ -3398,7 +3382,7 @@
     <row r="13" ht="90" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>PRP (Plasma) Hair Treatment</t>
+          <t>Hair Mesotherapy</t>
         </is>
       </c>
       <c r="B13" s="12" t="n"/>
@@ -3407,19 +3391,6 @@
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
-    </row>
-    <row r="14" ht="90" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>Hair Mesotherapy</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
